--- a/data/trans_dic/P25C$productsfarma_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,2</t>
+          <t>3,33; 15,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,87</t>
+          <t>0,9; 8,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 11,53</t>
+          <t>3,16; 10,84</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,6</t>
+          <t>1,02; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,04</t>
+          <t>0,28; 6,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,13</t>
+          <t>1,25; 6,32</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 18,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,59</t>
+          <t>1,25; 6,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,28</t>
+          <t>1,66; 9,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,88</t>
+          <t>1,72; 6,17</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,33</t>
+          <t>0,27; 4,52</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,7</t>
+          <t>0,99; 4,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,28</t>
+          <t>1,52; 4,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,04</t>
+          <t>1,33; 4,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4418; 18753</t>
+          <t>4106; 18854</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>582; 5118</t>
+          <t>586; 5637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5495; 21719</t>
+          <t>5955; 20419</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>965; 8027</t>
+          <t>952; 8383</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163; 3423</t>
+          <t>162; 3837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1894; 9202</t>
+          <t>1872; 9485</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 17558</t>
+          <t>0; 17176</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 19105</t>
+          <t>0; 18827</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2158; 12468</t>
+          <t>2375; 12287</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1245; 7329</t>
+          <t>1311; 7772</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4590; 15766</t>
+          <t>4616; 16553</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>0; 5623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>441; 6850</t>
+          <t>430; 7158</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1843</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1169</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9473; 39508</t>
+          <t>8344; 40431</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5266; 14121</t>
+          <t>5011; 13731</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16176; 47317</t>
+          <t>15611; 47807</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$productsfarma_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 15,28</t>
+          <t>3,46; 15,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,67</t>
+          <t>0,91; 7,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,84</t>
+          <t>3,08; 12,02</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,99</t>
+          <t>0,86; 7,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,77</t>
+          <t>0,69; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,32</t>
+          <t>1,42; 6,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>1,33; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,65</t>
+          <t>0,0; 18,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>1,38; 8,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,49</t>
+          <t>1,11; 5,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,84</t>
+          <t>1,71; 10,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,17</t>
+          <t>1,92; 6,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,52</t>
+          <t>0,25; 3,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,81</t>
+          <t>2,44; 5,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,16</t>
+          <t>1,48; 4,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,08</t>
+          <t>2,45; 4,92</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12138</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4106; 18854</t>
+          <t>4515; 20014</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>586; 5637</t>
+          <t>633; 5395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5955; 20419</t>
+          <t>6159; 24050</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4977</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>952; 8383</t>
+          <t>885; 7955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>162; 3837</t>
+          <t>437; 4790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1872; 9485</t>
+          <t>2342; 10213</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4935</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 17176</t>
+          <t>1397; 10461</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 4261</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 18827</t>
+          <t>1761; 10743</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9847</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2375; 12287</t>
+          <t>2350; 12543</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1311; 7772</t>
+          <t>1453; 8555</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4616; 16553</t>
+          <t>5685; 18184</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2340</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5623</t>
+          <t>0; 6440</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4235</t>
+          <t>0; 3927</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>430; 7158</t>
+          <t>435; 6382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>34237</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8344; 40431</t>
+          <t>15853; 37400</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5011; 13731</t>
+          <t>5300; 14804</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15611; 47807</t>
+          <t>24644; 49630</t>
         </is>
       </c>
     </row>
